--- a/data/trans_orig/P05A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>381059</t>
+          <t>379365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>414737</t>
+          <t>413475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>349852</t>
+          <t>349805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383910</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>742072</t>
+          <t>738312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>788205</t>
+          <t>789387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62684</t>
+          <t>63473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94588</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69096</t>
+          <t>71117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101956</t>
+          <t>103087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>140737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185425</t>
+          <t>188894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558408</t>
+          <t>556168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>602493</t>
+          <t>602016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435983</t>
+          <t>435423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479583</t>
+          <t>480650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006446</t>
+          <t>1005922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1070905</t>
+          <t>1069133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,61%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114767</t>
+          <t>114988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>156329</t>
+          <t>157708</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114346</t>
+          <t>113939</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155671</t>
+          <t>153702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>238729</t>
+          <t>239153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>299359</t>
+          <t>299346</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28338</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23013</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37834</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66672</t>
+          <t>70105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>485684</t>
+          <t>484204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>526974</t>
+          <t>525311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>472029</t>
+          <t>469683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>519589</t>
+          <t>519754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>968763</t>
+          <t>972262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1031996</t>
+          <t>1035472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95716</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136394</t>
+          <t>138307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116306</t>
+          <t>116970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159132</t>
+          <t>161751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226141</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282229</t>
+          <t>282496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43866</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71905</t>
+          <t>70836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55599</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88802</t>
+          <t>88474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>389420</t>
+          <t>389872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427374</t>
+          <t>427319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>357163</t>
+          <t>356076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>397618</t>
+          <t>396607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>754643</t>
+          <t>755848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>813480</t>
+          <t>811972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,61%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76249</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112813</t>
+          <t>112051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88913</t>
+          <t>89454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126301</t>
+          <t>126928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174788</t>
+          <t>175072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229768</t>
+          <t>227897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41911</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>59099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267381</t>
+          <t>266045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301680</t>
+          <t>300544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277016</t>
+          <t>277351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313006</t>
+          <t>313244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>554183</t>
+          <t>556616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>604384</t>
+          <t>606041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68081</t>
+          <t>68051</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>62589</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94253</t>
+          <t>92843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138911</t>
+          <t>139204</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>184986</t>
+          <t>182783</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>61334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206666</t>
+          <t>206334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235446</t>
+          <t>235270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>234967</t>
+          <t>233533</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>264820</t>
+          <t>264020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448422</t>
+          <t>448628</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>492332</t>
+          <t>490353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>49123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87763</t>
+          <t>89491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117066</t>
+          <t>118035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158771</t>
+          <t>158308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>29007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145668</t>
+          <t>148158</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170728</t>
+          <t>170643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>245972</t>
+          <t>244690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>276360</t>
+          <t>277076</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400457</t>
+          <t>400110</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>439584</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>34653</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59031</t>
+          <t>56739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,82 +3597,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>27,15%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>62187</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>48985</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>79583</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>107732</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>90206</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>128549</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>16,61%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>62187</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>48515</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>78591</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>107732</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>89104</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>125650</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9577</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2514451</t>
+          <t>2509516</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2606516</t>
+          <t>2606784</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2455923</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2556986</t>
+          <t>2556397</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4996877</t>
+          <t>4998598</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5135074</t>
+          <t>5138122</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>569288</t>
+          <t>568350</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>655375</t>
+          <t>659665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>632750</t>
+          <t>632594</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>720408</t>
+          <t>724066</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1225227</t>
+          <t>1228724</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1355834</t>
+          <t>1357246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>78417</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>115947</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165081</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>217956</t>
+          <t>216051</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>253691</t>
+          <t>253328</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>320738</t>
+          <t>316534</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372378</t>
+          <t>370815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>402367</t>
+          <t>401863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>352644</t>
+          <t>352437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>381615</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>735350</t>
+          <t>733371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>777393</t>
+          <t>777319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96158</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137346</t>
+          <t>138323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575418</t>
+          <t>574086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>610821</t>
+          <t>611253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488875</t>
+          <t>488532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>525851</t>
+          <t>525357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1073271</t>
+          <t>1074086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1128174</t>
+          <t>1125814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57726</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89775</t>
+          <t>90591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>95380</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123372</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174636</t>
+          <t>174086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37013</t>
+          <t>36868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59475</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>550644</t>
+          <t>552111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>588285</t>
+          <t>589030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550339</t>
+          <t>549031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592419</t>
+          <t>593377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1113183</t>
+          <t>1113361</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1172515</t>
+          <t>1170452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>70477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106373</t>
+          <t>104441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89169</t>
+          <t>88325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129145</t>
+          <t>130236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169831</t>
+          <t>168630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223223</t>
+          <t>221327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>34622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>61787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>485317</t>
+          <t>483300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524951</t>
+          <t>525536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>479013</t>
+          <t>476008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>520374</t>
+          <t>517297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>975118</t>
+          <t>977392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1033044</t>
+          <t>1032233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67102</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106340</t>
+          <t>106836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64899</t>
+          <t>66720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>104432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146155</t>
+          <t>144664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198253</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41607</t>
+          <t>41802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,47 +6260,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>51571</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>38345</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>67322</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>51571</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>38357</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>68948</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355486</t>
+          <t>356653</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>385153</t>
+          <t>385972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>357815</t>
+          <t>357518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>390912</t>
+          <t>389431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>723212</t>
+          <t>724392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>766656</t>
+          <t>769438</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74050</t>
+          <t>73923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88276</t>
+          <t>85922</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128469</t>
+          <t>127333</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>23844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>33251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>237764</t>
+          <t>238727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266682</t>
+          <t>268516</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>280705</t>
+          <t>279627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>308430</t>
+          <t>307279</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>523268</t>
+          <t>525640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>566089</t>
+          <t>565600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74548</t>
+          <t>76308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>113846</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198612</t>
+          <t>198460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221984</t>
+          <t>222207</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>321753</t>
+          <t>320819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>349490</t>
+          <t>349218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>529699</t>
+          <t>528473</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>567792</t>
+          <t>563698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41475</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>60698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57944</t>
+          <t>60456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93810</t>
+          <t>94308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2849446</t>
+          <t>2846352</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2938008</t>
+          <t>2933474</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2908589</t>
+          <t>2906474</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3000181</t>
+          <t>2997835</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5792135</t>
+          <t>5788594</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5915748</t>
+          <t>5912702</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>393689</t>
+          <t>397776</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>477121</t>
+          <t>475595</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>430946</t>
+          <t>429179</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>515749</t>
+          <t>511808</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>846882</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>961138</t>
+          <t>959629</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>101019</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>180840</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>242839</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358565</t>
+          <t>357267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>386008</t>
+          <t>384347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324612</t>
+          <t>324041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>353315</t>
+          <t>352719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>691600</t>
+          <t>693225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>730176</t>
+          <t>732881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>46299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32360</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58570</t>
+          <t>58206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62555</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95856</t>
+          <t>94648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496565</t>
+          <t>495500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>529055</t>
+          <t>529045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466919</t>
+          <t>465189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498109</t>
+          <t>497830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>971210</t>
+          <t>972203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017026</t>
+          <t>1018550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78813</t>
+          <t>77756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74167</t>
+          <t>76318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103001</t>
+          <t>103216</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>144797</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>563693</t>
+          <t>565389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>600083</t>
+          <t>599190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550258</t>
+          <t>549653</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584874</t>
+          <t>584306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124292</t>
+          <t>1126698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1178029</t>
+          <t>1176440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81739</t>
+          <t>81401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>58719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89145</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115048</t>
+          <t>117426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>159760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29307</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>25110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546379</t>
+          <t>546754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>580604</t>
+          <t>581404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>538103</t>
+          <t>539628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574470</t>
+          <t>576177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1100705</t>
+          <t>1097516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1149345</t>
+          <t>1148281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51276</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81900</t>
+          <t>82513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>49803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81598</t>
+          <t>79882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>107836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148969</t>
+          <t>153622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>391422</t>
+          <t>388118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>422967</t>
+          <t>422154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>401440</t>
+          <t>403062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>434702</t>
+          <t>436352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>801459</t>
+          <t>803167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>848951</t>
+          <t>849887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41231</t>
+          <t>41734</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71458</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91086</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131919</t>
+          <t>132530</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>48075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283699</t>
+          <t>282060</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307193</t>
+          <t>306354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307379</t>
+          <t>306932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333399</t>
+          <t>334390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>596719</t>
+          <t>600012</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>632639</t>
+          <t>635575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45052</t>
+          <t>46381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56051</t>
+          <t>57072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62174</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94921</t>
+          <t>93357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>217592</t>
+          <t>217252</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235868</t>
+          <t>236321</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>338314</t>
+          <t>335550</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365564</t>
+          <t>365042</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>563166</t>
+          <t>561605</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>597014</t>
+          <t>596850</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34445</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81079</t>
+          <t>78058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2928051</t>
+          <t>2930651</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3006962</t>
+          <t>3006579</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3005538</t>
+          <t>3001524</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3088312</t>
+          <t>3085756</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5958420</t>
+          <t>5953218</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6071663</t>
+          <t>6070705</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>300915</t>
+          <t>303176</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>374507</t>
+          <t>374638</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>339054</t>
+          <t>338626</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>417635</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>665675</t>
+          <t>661186</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>769525</t>
+          <t>764242</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>96501</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>87817</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>130708</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>159478</t>
+          <t>158586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>215459</t>
+          <t>216227</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>344932</t>
+          <t>344189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381261</t>
+          <t>382130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246701</t>
+          <t>245679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282950</t>
+          <t>282319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608264</t>
+          <t>605987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>657077</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56997</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85044</t>
+          <t>85309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364247</t>
+          <t>362973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395610</t>
+          <t>395303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471353</t>
+          <t>470299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495839</t>
+          <t>495284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>842138</t>
+          <t>841927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885281</t>
+          <t>883363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44067</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74480</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>465261</t>
+          <t>463782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>494993</t>
+          <t>493983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>519708</t>
+          <t>518697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>549195</t>
+          <t>548348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1013989</t>
+          <t>1013990</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>990040</t>
+          <t>994812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1035261</t>
+          <t>1036185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30721</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57751</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>26731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>51072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64702</t>
+          <t>63890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101347</t>
+          <t>99152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>42099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>796726</t>
+          <t>799215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>861616</t>
+          <t>864488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622713</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>651117</t>
+          <t>651998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1432454</t>
+          <t>1431932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1515159</t>
+          <t>1517848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66188</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43724</t>
+          <t>42944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>67252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>59623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122811</t>
+          <t>124111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>48543</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>499201</t>
+          <t>499495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>523936</t>
+          <t>525630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>468380</t>
+          <t>467140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>490606</t>
+          <t>490926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>976101</t>
+          <t>973969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1008725</t>
+          <t>1010980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43757</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64183</t>
+          <t>64274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>77724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>108688</t>
+          <t>110837</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>328935</t>
+          <t>328736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>346210</t>
+          <t>345902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>553676</t>
+          <t>551963</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>594132</t>
+          <t>595009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>889028</t>
+          <t>889964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>947796</t>
+          <t>943606</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71962</t>
+          <t>70375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>252834</t>
+          <t>253078</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>267784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>385069</t>
+          <t>384619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>400345</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>641432</t>
+          <t>643370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>665538</t>
+          <t>664116</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54466</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3123610</t>
+          <t>3126460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3234362</t>
+          <t>3235166</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3331228</t>
+          <t>3323384</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3436876</t>
+          <t>3429221</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6478398</t>
+          <t>6472644</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6622039</t>
+          <t>6617418</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>170623</t>
+          <t>163655</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>257336</t>
+          <t>254831</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>210956</t>
+          <t>214342</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>295674</t>
+          <t>304770</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>418463</t>
+          <t>419031</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>535387</t>
+          <t>538389</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>94070</t>
+          <t>96609</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>172434</t>
+          <t>174157</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>379365</t>
+          <t>379683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>413475</t>
+          <t>413892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>349805</t>
+          <t>349396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383297</t>
+          <t>382998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>738312</t>
+          <t>740503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>789387</t>
+          <t>788933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94866</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71117</t>
+          <t>70764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>102396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140737</t>
+          <t>139527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188894</t>
+          <t>185643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556168</t>
+          <t>557781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>602016</t>
+          <t>602661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435423</t>
+          <t>433404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480650</t>
+          <t>481145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005922</t>
+          <t>1003202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1069133</t>
+          <t>1069318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114988</t>
+          <t>114187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>157708</t>
+          <t>157178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>112313</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153702</t>
+          <t>154578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>239153</t>
+          <t>239686</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>299346</t>
+          <t>302232</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70105</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>484204</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>525311</t>
+          <t>524971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>469683</t>
+          <t>471378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>519754</t>
+          <t>518751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>972262</t>
+          <t>969931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1035472</t>
+          <t>1032597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96561</t>
+          <t>98353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138307</t>
+          <t>138626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161751</t>
+          <t>159463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224746</t>
+          <t>222426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282496</t>
+          <t>281907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>42582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70836</t>
+          <t>73158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56080</t>
+          <t>54725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88474</t>
+          <t>88118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>389872</t>
+          <t>388499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427319</t>
+          <t>427366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>356076</t>
+          <t>355534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>396607</t>
+          <t>394757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>755848</t>
+          <t>758556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811972</t>
+          <t>814315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75459</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>91517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126928</t>
+          <t>127346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175072</t>
+          <t>176390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>226722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>25150</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59099</t>
+          <t>60800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266045</t>
+          <t>266875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300544</t>
+          <t>300891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277351</t>
+          <t>277086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313244</t>
+          <t>311257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>556616</t>
+          <t>556298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606041</t>
+          <t>602753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68051</t>
+          <t>67541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>100673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>62600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92843</t>
+          <t>94269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>139204</t>
+          <t>140108</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>182783</t>
+          <t>182229</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40557</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61334</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206334</t>
+          <t>206665</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235270</t>
+          <t>235273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>233533</t>
+          <t>233281</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>264020</t>
+          <t>264536</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448628</t>
+          <t>449815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>490353</t>
+          <t>492337</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>49170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60770</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118035</t>
+          <t>116858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158308</t>
+          <t>156405</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39649</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148158</t>
+          <t>146595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170643</t>
+          <t>169190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244690</t>
+          <t>245852</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>277076</t>
+          <t>277576</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400110</t>
+          <t>400045</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>439869</t>
+          <t>439865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>35314</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56739</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>48552</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>78164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>88932</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128549</t>
+          <t>126907</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2509516</t>
+          <t>2511051</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2606784</t>
+          <t>2605799</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2455923</t>
+          <t>2454741</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2556397</t>
+          <t>2558527</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4998598</t>
+          <t>4998356</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5138122</t>
+          <t>5135256</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>568350</t>
+          <t>569910</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>659665</t>
+          <t>659460</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>632594</t>
+          <t>632194</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>724066</t>
+          <t>725107</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1228724</t>
+          <t>1233066</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1357246</t>
+          <t>1353572</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>78243</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>115575</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>163632</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>216051</t>
+          <t>220142</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>253797</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>316534</t>
+          <t>318891</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>370815</t>
+          <t>372876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>401863</t>
+          <t>402128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>352437</t>
+          <t>352353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383871</t>
+          <t>381513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>733371</t>
+          <t>733984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>777319</t>
+          <t>776338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>50116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80120</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,82 +4744,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>52132</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40776</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68304</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>115520</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>97122</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>139237</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52132</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38525</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66972</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>115520</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>96099</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>138323</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>574086</t>
+          <t>574332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>611253</t>
+          <t>611896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488532</t>
+          <t>487743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>525357</t>
+          <t>524855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1074086</t>
+          <t>1069507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1125814</t>
+          <t>1125435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58663</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90591</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>62199</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95380</t>
+          <t>94240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128203</t>
+          <t>128476</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174086</t>
+          <t>174747</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58450</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>552111</t>
+          <t>551477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>589030</t>
+          <t>589373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>549031</t>
+          <t>548388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>593377</t>
+          <t>592106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1113361</t>
+          <t>1114693</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1170452</t>
+          <t>1173384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70477</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104441</t>
+          <t>106924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88325</t>
+          <t>90596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130236</t>
+          <t>130672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168630</t>
+          <t>168928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221327</t>
+          <t>220529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34622</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61787</t>
+          <t>62209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483300</t>
+          <t>482996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>525536</t>
+          <t>526649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>476008</t>
+          <t>477097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>517297</t>
+          <t>519631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>977392</t>
+          <t>977356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1032233</t>
+          <t>1035257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>68333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106836</t>
+          <t>107736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>65689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>102701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144664</t>
+          <t>142095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195503</t>
+          <t>196004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41802</t>
+          <t>43750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67322</t>
+          <t>67083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356653</t>
+          <t>357042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>385972</t>
+          <t>386386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>357518</t>
+          <t>358693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>389431</t>
+          <t>391354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>724392</t>
+          <t>724893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>769438</t>
+          <t>768831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64719</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73923</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85922</t>
+          <t>88009</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127333</t>
+          <t>127586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238727</t>
+          <t>237691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>268516</t>
+          <t>267685</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>279627</t>
+          <t>279989</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>307279</t>
+          <t>307862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>525640</t>
+          <t>526854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>565600</t>
+          <t>568188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32937</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>62401</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34951</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>59794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76308</t>
+          <t>75631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113846</t>
+          <t>111999</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32939</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198460</t>
+          <t>198440</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222207</t>
+          <t>223241</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>320819</t>
+          <t>321459</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>349218</t>
+          <t>348915</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>528473</t>
+          <t>526872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>563698</t>
+          <t>564847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60698</t>
+          <t>60239</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60456</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94308</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23668</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2846352</t>
+          <t>2851544</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2933474</t>
+          <t>2936555</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2906474</t>
+          <t>2906297</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2997835</t>
+          <t>3000164</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5788594</t>
+          <t>5788928</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5912702</t>
+          <t>5913425</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>397776</t>
+          <t>400531</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475595</t>
+          <t>473127</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>429179</t>
+          <t>427551</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>511808</t>
+          <t>508731</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>846882</t>
+          <t>845079</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>959629</t>
+          <t>963012</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>67542</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>108082</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>101019</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148553</t>
+          <t>149023</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>183156</t>
+          <t>182766</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>242839</t>
+          <t>239735</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357267</t>
+          <t>359388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384347</t>
+          <t>385802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324041</t>
+          <t>326310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352719</t>
+          <t>352494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>693225</t>
+          <t>693901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>732881</t>
+          <t>732042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23134</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>58036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>60703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94648</t>
+          <t>94782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>36301</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495500</t>
+          <t>495479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>529045</t>
+          <t>528652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465189</t>
+          <t>467816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497830</t>
+          <t>498558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972203</t>
+          <t>973775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018550</t>
+          <t>1018850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77756</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76318</t>
+          <t>74102</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103216</t>
+          <t>101301</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>143403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>565389</t>
+          <t>566190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>599190</t>
+          <t>600222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>549653</t>
+          <t>550295</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584306</t>
+          <t>585080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1126698</t>
+          <t>1125985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1176440</t>
+          <t>1174376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51591</t>
+          <t>49944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81401</t>
+          <t>81348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58719</t>
+          <t>57226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117426</t>
+          <t>117263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159760</t>
+          <t>160460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50447</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546754</t>
+          <t>548657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>581404</t>
+          <t>581795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>539628</t>
+          <t>539142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>576177</t>
+          <t>573875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1097516</t>
+          <t>1097549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1148281</t>
+          <t>1148745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50190</t>
+          <t>49268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82513</t>
+          <t>80098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79882</t>
+          <t>82817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107836</t>
+          <t>109529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153622</t>
+          <t>155384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>389416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>422154</t>
+          <t>421667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>403062</t>
+          <t>401911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>436352</t>
+          <t>435295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>803167</t>
+          <t>804369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>849887</t>
+          <t>850624</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>69550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>72207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>132530</t>
+          <t>132421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282060</t>
+          <t>283326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>306354</t>
+          <t>306687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306932</t>
+          <t>306923</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334390</t>
+          <t>333963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>600012</t>
+          <t>597882</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>635575</t>
+          <t>634183</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46381</t>
+          <t>45409</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>32180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57072</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>60620</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93357</t>
+          <t>94510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>217252</t>
+          <t>217589</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236321</t>
+          <t>235430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>335550</t>
+          <t>337802</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365042</t>
+          <t>366361</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>561605</t>
+          <t>562262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>596850</t>
+          <t>596814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35227</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53936</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47258</t>
+          <t>47272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78058</t>
+          <t>78218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2930651</t>
+          <t>2930855</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3006579</t>
+          <t>3006807</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3001524</t>
+          <t>3002458</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3085756</t>
+          <t>3084034</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5953218</t>
+          <t>5949200</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6070705</t>
+          <t>6068194</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>303176</t>
+          <t>301875</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>374638</t>
+          <t>372033</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>338626</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>417635</t>
+          <t>415241</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,47 +11854,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>714186</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>663978</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>772298</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>714186</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>661186</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>764242</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>64735</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101193</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>87817</t>
+          <t>87966</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>132957</t>
+          <t>130567</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>158586</t>
+          <t>161228</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>216227</t>
+          <t>212767</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>367470</t>
+          <t>377948</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>344189</t>
+          <t>357843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382130</t>
+          <t>391946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>267667</t>
+          <t>311232</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245679</t>
+          <t>290869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282319</t>
+          <t>326190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>635137</t>
+          <t>689181</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>605987</t>
+          <t>659449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>658237</t>
+          <t>711201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>42829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55400</t>
+          <t>60442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60019</t>
+          <t>64522</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85309</t>
+          <t>93451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23337</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>381727</t>
+          <t>424569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362973</t>
+          <t>401851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395303</t>
+          <t>439464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>483123</t>
+          <t>467519</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470299</t>
+          <t>454947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495284</t>
+          <t>477861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>864850</t>
+          <t>892088</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841927</t>
+          <t>870080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883363</t>
+          <t>913258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28281</t>
+          <t>37529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>40646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>67050</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>88226</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,67 +13094,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>19485</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>11852</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>33701</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>17483</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>9490</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>33088</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>480390</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>463782</t>
+          <t>533885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493983</t>
+          <t>568112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533599</t>
+          <t>554800</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>518697</t>
+          <t>540611</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>548348</t>
+          <t>568275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1013990</t>
+          <t>1107760</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>994812</t>
+          <t>1084723</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1036185</t>
+          <t>1126634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>51446</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58040</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51072</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81816</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63890</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99152</t>
+          <t>117180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42099</t>
+          <t>47896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>827242</t>
+          <t>634569</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>799215</t>
+          <t>615928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>864488</t>
+          <t>650742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>637197</t>
+          <t>648402</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623300</t>
+          <t>634453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>651998</t>
+          <t>661399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1464437</t>
+          <t>1282971</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1431932</t>
+          <t>1260716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1517848</t>
+          <t>1301661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42668</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64414</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>55410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>78600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>97975</t>
+          <t>113431</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>95819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124111</t>
+          <t>132142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886676</t>
+          <t>699431</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886676</t>
+          <t>699431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886676</t>
+          <t>699431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>710879</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>710879</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>710879</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597554</t>
+          <t>1435430</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597554</t>
+          <t>1435430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597554</t>
+          <t>1435430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>512941</t>
+          <t>559421</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>499495</t>
+          <t>545266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>525630</t>
+          <t>569822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>480427</t>
+          <t>531417</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>467140</t>
+          <t>519793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>490926</t>
+          <t>543896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>993368</t>
+          <t>1090838</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>973969</t>
+          <t>1072761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1010980</t>
+          <t>1107330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43167</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>71983</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>103192</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77724</t>
+          <t>88793</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110837</t>
+          <t>120910</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,22 +14497,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107907</t>
+          <t>1216841</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107907</t>
+          <t>1216841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107907</t>
+          <t>1216841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>337875</t>
+          <t>374383</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>328736</t>
+          <t>364684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>345902</t>
+          <t>383171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>573958</t>
+          <t>401927</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>551963</t>
+          <t>392215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>595009</t>
+          <t>409340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>911833</t>
+          <t>776309</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>889964</t>
+          <t>763181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>943606</t>
+          <t>788118</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>34630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52226</t>
+          <t>56573</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>45673</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70375</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,67 +14918,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>12673</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>7751</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>19385</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>11891</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>19367</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607785</t>
+          <t>438476</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607785</t>
+          <t>438476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607785</t>
+          <t>438476</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975950</t>
+          <t>845555</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975950</t>
+          <t>845555</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975950</t>
+          <t>845555</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>261374</t>
+          <t>285588</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>253078</t>
+          <t>276459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267784</t>
+          <t>292909</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,67 +15148,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>393377</t>
+          <t>427306</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>384619</t>
+          <t>417477</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>400794</t>
+          <t>435840</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>89,86%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>712894</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>699799</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>725321</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>654750</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>643370</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>664116</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -15339,17 +15339,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3169019</t>
+          <t>3209439</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3126460</t>
+          <t>3171024</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3235166</t>
+          <t>3248306</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3369346</t>
+          <t>3342604</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3323384</t>
+          <t>3308476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3429221</t>
+          <t>3377601</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6538366</t>
+          <t>6552042</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6472644</t>
+          <t>6500496</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6617418</t>
+          <t>6602458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>219493</t>
+          <t>245889</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>163655</t>
+          <t>211752</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>254831</t>
+          <t>279937</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>262448</t>
+          <t>306385</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>214342</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>304770</t>
+          <t>339284</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>481941</t>
+          <t>552274</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>419031</t>
+          <t>508182</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>538389</t>
+          <t>601828</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>68846</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>92096</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>75938</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59914</t>
+          <t>68824</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>96609</t>
+          <t>103361</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>144785</t>
+          <t>157147</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>121351</t>
+          <t>133461</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>174157</t>
+          <t>182330</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457358</t>
+          <t>3528195</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3707732</t>
+          <t>3733269</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7165091</t>
+          <t>7261464</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
